--- a/output/pdf_financials_xlsx/ABR.xlsx
+++ b/output/pdf_financials_xlsx/ABR.xlsx
@@ -1186,7 +1186,7 @@
         <v>-0.154912</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.343456</v>
@@ -1454,7 +1454,7 @@
         <v>-0.154912</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.343456</v>
@@ -1610,7 +1610,7 @@
         <v>-0.154912</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.343456</v>
@@ -1860,7 +1860,7 @@
         <v>-0.154912</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.343456</v>
@@ -1964,7 +1964,7 @@
         <v>-0.154912</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.343456</v>
@@ -2098,7 +2098,7 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5402,31 +5402,31 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.171923</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.171923</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.171923</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.171923</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.281746</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.281746</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.350984</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.428641</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.961407</v>
       </c>
     </row>
     <row r="93">
@@ -9013,7 +9013,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10510,7 +10514,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11038,7 +11046,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11768,7 +11780,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -12221,7 +12237,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13125,7 +13145,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -13584,7 +13608,11 @@
           <t>Share-based payment reserve (note 6)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -35755,7 +35783,7 @@
         </is>
       </c>
       <c r="H311" s="5" t="n">
-        <v>0.116008</v>
+        <v>-0.116008</v>
       </c>
       <c r="I311" s="5" t="n">
         <v>-0.343456</v>

--- a/output/pdf_financials_xlsx/ABR.xlsx
+++ b/output/pdf_financials_xlsx/ABR.xlsx
@@ -907,7 +907,7 @@
         <v>2.569653</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.140745</v>
+        <v>0.822462</v>
       </c>
     </row>
     <row r="11">
@@ -959,7 +959,7 @@
         <v>-2.569653</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.140745</v>
+        <v>-0.822462</v>
       </c>
     </row>
     <row r="12">
@@ -975,13 +975,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00312</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000511</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.302385</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.169995</v>
       </c>
     </row>
     <row r="13">
@@ -1857,13 +1857,13 @@
         <v>-0.167012</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.154912</v>
+        <v>-0.158032</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.116008</v>
+        <v>-0.118031</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.343456</v>
+        <v>-0.343967</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.031201</v>
@@ -1890,10 +1890,10 @@
         <v>-0.411603</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.547562</v>
+        <v>-1.849947</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.473401</v>
+        <v>0.303406</v>
       </c>
     </row>
     <row r="28">
@@ -1961,13 +1961,13 @@
         <v>-0.167012</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.154912</v>
+        <v>-0.158032</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.116008</v>
+        <v>-0.118031</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.343456</v>
+        <v>-0.343967</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.031201</v>
@@ -1994,10 +1994,10 @@
         <v>-0.411603</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.547562</v>
+        <v>-1.849947</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.473401</v>
+        <v>0.303406</v>
       </c>
     </row>
     <row r="30">
@@ -2236,16 +2236,16 @@
         <v>0.561467</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.216944</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.128452</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033965</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022807</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.002452</v>
@@ -2269,10 +2269,10 @@
         <v>4.761035</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.358253</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.457409</v>
       </c>
     </row>
     <row r="35">
@@ -2340,16 +2340,16 @@
         <v>0.561467</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.216944</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.128452</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033965</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022807</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.002452</v>
@@ -2373,10 +2373,10 @@
         <v>4.761035</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>5.380301</v>
+        <v>7.738554</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.5</v>
+        <v>0.957409</v>
       </c>
     </row>
     <row r="37">
@@ -2964,16 +2964,16 @@
         <v>0.073687</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.230337</v>
+        <v>0.013393</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.130332</v>
+        <v>0.00188</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.036945</v>
+        <v>0.00298</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.023807</v>
+        <v>0.001</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -2997,10 +2997,10 @@
         <v>0.006073</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.358253</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.461242</v>
+        <v>0.003833</v>
       </c>
     </row>
     <row r="49">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -31027,7 +31027,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -31096,10 +31096,10 @@
         </is>
       </c>
       <c r="R258" s="5" t="n">
-        <v>-2.569653</v>
+        <v>2.569653</v>
       </c>
       <c r="S258" s="5" t="n">
-        <v>-0.822462</v>
+        <v>0.822462</v>
       </c>
     </row>
     <row r="259">
@@ -31120,7 +31120,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">

--- a/output/pdf_financials_xlsx/ABR.xlsx
+++ b/output/pdf_financials_xlsx/ABR.xlsx
@@ -4015,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.01043</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>0.010188</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.025191</v>
+        <v>0.032691</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.01782</v>
+        <v>0.03282</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.046906</v>
+        <v>0.091906</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.011855</v>
+        <v>0.022285</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.009545</v>
@@ -5834,46 +5834,46 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.000993</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.010819</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.000578</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001136</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.000346</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.001138</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000849</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000485</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001082</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.000993</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000103</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00908</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>-0.165712</v>
+        <v>-0.216134</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>-0.14654</v>
+        <v>-0.149322</v>
       </c>
     </row>
     <row r="102">
@@ -6122,28 +6122,28 @@
         <v>-0.020355</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.101801</v>
+        <v>0.100952</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.096288</v>
+        <v>-0.096773</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.134982</v>
+        <v>-0.136064</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.163922</v>
+        <v>0.164915</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.031435</v>
+        <v>-0.031538</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.049605</v>
+        <v>0.040525</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.117523</v>
+        <v>-0.167945</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.10633</v>
+        <v>-0.109112</v>
       </c>
     </row>
     <row r="107">
@@ -17105,7 +17105,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -21113,7 +21117,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -23670,7 +23678,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -23759,7 +23771,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -25494,7 +25510,11 @@
           <t>GST / HST receivable</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -28166,7 +28186,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -28902,7 +28926,11 @@
           <t>Common shares issued for cash (note 9)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -29733,7 +29761,11 @@
           <t>Common shares issued for cash (note 10) 861,207</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
